--- a/crossrc_banco_de_dados.xlsx
+++ b/crossrc_banco_de_dados.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0c3db7787cc94580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alunos" sheetId="2" r:id="R2cc6cdb09ab349d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pagamentos" sheetId="3" r:id="Ra4dc384706404a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="avaliacoes" sheetId="4" r:id="R790b9e29f7a24532"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vendas" sheetId="5" r:id="Re0125fcedfe64b3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turmas" sheetId="6" r:id="Rfc8a2e3216c9443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfa7a1e70e8084ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alunos" sheetId="2" r:id="R75c7bd0001a342c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pagamentos" sheetId="3" r:id="Rf5eb3f537c514b81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="avaliacoes" sheetId="4" r:id="R149eb0ee71454313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vendas" sheetId="5" r:id="R545acd91a16b449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turmas" sheetId="6" r:id="Rd5daa84123ef417b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47,7 +47,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -64,6 +64,11 @@
         <x:fgColor rgb="B7FF00"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="111111"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -72,7 +77,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -129,6 +134,17 @@
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -466,51 +482,71 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.270000457763672" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.059999942779541" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.170000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.539999961853027" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="6.730000019073486" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10.359999656677246" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17.360000610351562" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16.690000534057617" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12.520000457763672" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18.709999084472656" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="30.81999969482422" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="11.979999542236328" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B1" s="20" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>foto</x:v>
       </x:c>
-      <x:c r="C1" s="20" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>nome</x:v>
       </x:c>
-      <x:c r="D1" s="20" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>telefone</x:v>
       </x:c>
-      <x:c r="E1" s="20" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>nascimento</x:v>
       </x:c>
-      <x:c r="F1" s="20" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>turma</x:v>
       </x:c>
-      <x:c r="G1" s="20" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="H1" s="20" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>valor</x:v>
       </x:c>
-      <x:c r="I1" s="20" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>vencimento</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>matricula</x:v>
       </x:c>
-      <x:c r="K1" s="20" t="str">
+      <x:c r="K1" s="29" t="str">
+        <x:v>responsavelNome</x:v>
+      </x:c>
+      <x:c r="L1" s="32" t="str">
+        <x:v>responsavelTelefone</x:v>
+      </x:c>
+      <x:c r="M1" s="32" t="str">
+        <x:v>responsavelCpf</x:v>
+      </x:c>
+      <x:c r="N1" s="32" t="str">
+        <x:v>responsavelParentesco</x:v>
+      </x:c>
+      <x:c r="O1" s="32" t="str">
+        <x:v>responsavelObs</x:v>
+      </x:c>
+      <x:c r="P1" s="32" t="str">
         <x:v>obs</x:v>
       </x:c>
     </x:row>
@@ -518,7 +554,7 @@
       <x:c r="A2" s="21" t="str">
         <x:v>aluno_exemplo_1</x:v>
       </x:c>
-      <x:c r="B2" s="21" t="str"/>
+      <x:c r="B2" s="21"/>
       <x:c r="C2" s="21" t="str">
         <x:v>João Silva</x:v>
       </x:c>
@@ -537,13 +573,28 @@
       <x:c r="H2" s="24" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="I2" s="21" t="n">
-        <x:v>10</x:v>
+      <x:c r="I2" s="26" t="str">
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="J2" s="26" t="str">
         <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="K2" s="21" t="str">
+        <x:v>Responsável Exemplo</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>35999990000</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>000.000.000-00</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>Aluno é o cliente</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>Contato principal para cobrança</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
         <x:v>Aluno exemplo</x:v>
       </x:c>
     </x:row>
@@ -551,7 +602,7 @@
       <x:c r="A3" s="21" t="str">
         <x:v>aluno_exemplo_2</x:v>
       </x:c>
-      <x:c r="B3" s="21" t="str"/>
+      <x:c r="B3" s="21"/>
       <x:c r="C3" s="21" t="str">
         <x:v>Maria Oliveira</x:v>
       </x:c>
@@ -570,13 +621,26 @@
       <x:c r="H3" s="24" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="I3" s="21" t="n">
-        <x:v>15</x:v>
+      <x:c r="I3" s="26" t="str">
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="J3" s="26" t="str">
         <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="K3" s="21" t="str">
+        <x:v>Mãe da Maria</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>35999998888</x:v>
+      </x:c>
+      <x:c r="M3" t="str"/>
+      <x:c r="N3" t="str">
+        <x:v>Mãe</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>Autorizações e avisos pelo responsável</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
         <x:v>Aluno exemplo</x:v>
       </x:c>
     </x:row>
@@ -589,7 +653,7 @@
       <x:c r="F4" s="21"/>
       <x:c r="G4" s="21"/>
       <x:c r="H4" s="24"/>
-      <x:c r="I4" s="21"/>
+      <x:c r="I4" s="26"/>
       <x:c r="J4" s="26"/>
       <x:c r="K4" s="21"/>
     </x:row>
@@ -602,7 +666,7 @@
       <x:c r="F5" s="21"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="24"/>
-      <x:c r="I5" s="21"/>
+      <x:c r="I5" s="26"/>
       <x:c r="J5" s="26"/>
       <x:c r="K5" s="21"/>
     </x:row>
@@ -615,7 +679,7 @@
       <x:c r="F6" s="21"/>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="24"/>
-      <x:c r="I6" s="21"/>
+      <x:c r="I6" s="26"/>
       <x:c r="J6" s="26"/>
       <x:c r="K6" s="21"/>
     </x:row>
@@ -628,7 +692,7 @@
       <x:c r="F7" s="21"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="24"/>
-      <x:c r="I7" s="21"/>
+      <x:c r="I7" s="26"/>
       <x:c r="J7" s="26"/>
       <x:c r="K7" s="21"/>
     </x:row>
@@ -641,7 +705,7 @@
       <x:c r="F8" s="21"/>
       <x:c r="G8" s="21"/>
       <x:c r="H8" s="24"/>
-      <x:c r="I8" s="21"/>
+      <x:c r="I8" s="26"/>
       <x:c r="J8" s="26"/>
       <x:c r="K8" s="21"/>
     </x:row>
@@ -654,7 +718,7 @@
       <x:c r="F9" s="21"/>
       <x:c r="G9" s="21"/>
       <x:c r="H9" s="24"/>
-      <x:c r="I9" s="21"/>
+      <x:c r="I9" s="26"/>
       <x:c r="J9" s="26"/>
       <x:c r="K9" s="21"/>
     </x:row>
@@ -667,7 +731,7 @@
       <x:c r="F10" s="21"/>
       <x:c r="G10" s="21"/>
       <x:c r="H10" s="24"/>
-      <x:c r="I10" s="21"/>
+      <x:c r="I10" s="26"/>
       <x:c r="J10" s="26"/>
       <x:c r="K10" s="21"/>
     </x:row>
@@ -680,7 +744,7 @@
       <x:c r="F11" s="21"/>
       <x:c r="G11" s="21"/>
       <x:c r="H11" s="24"/>
-      <x:c r="I11" s="21"/>
+      <x:c r="I11" s="26"/>
       <x:c r="J11" s="26"/>
       <x:c r="K11" s="21"/>
     </x:row>
@@ -693,7 +757,7 @@
       <x:c r="F12" s="21"/>
       <x:c r="G12" s="21"/>
       <x:c r="H12" s="24"/>
-      <x:c r="I12" s="21"/>
+      <x:c r="I12" s="26"/>
       <x:c r="J12" s="26"/>
       <x:c r="K12" s="21"/>
     </x:row>
@@ -706,7 +770,7 @@
       <x:c r="F13" s="21"/>
       <x:c r="G13" s="21"/>
       <x:c r="H13" s="24"/>
-      <x:c r="I13" s="21"/>
+      <x:c r="I13" s="26"/>
       <x:c r="J13" s="26"/>
       <x:c r="K13" s="21"/>
     </x:row>
@@ -719,7 +783,7 @@
       <x:c r="F14" s="21"/>
       <x:c r="G14" s="21"/>
       <x:c r="H14" s="24"/>
-      <x:c r="I14" s="21"/>
+      <x:c r="I14" s="26"/>
       <x:c r="J14" s="26"/>
       <x:c r="K14" s="21"/>
     </x:row>
@@ -732,7 +796,7 @@
       <x:c r="F15" s="21"/>
       <x:c r="G15" s="21"/>
       <x:c r="H15" s="24"/>
-      <x:c r="I15" s="21"/>
+      <x:c r="I15" s="26"/>
       <x:c r="J15" s="26"/>
       <x:c r="K15" s="21"/>
     </x:row>
@@ -745,7 +809,7 @@
       <x:c r="F16" s="21"/>
       <x:c r="G16" s="21"/>
       <x:c r="H16" s="24"/>
-      <x:c r="I16" s="21"/>
+      <x:c r="I16" s="26"/>
       <x:c r="J16" s="26"/>
       <x:c r="K16" s="21"/>
     </x:row>
@@ -758,7 +822,7 @@
       <x:c r="F17" s="21"/>
       <x:c r="G17" s="21"/>
       <x:c r="H17" s="24"/>
-      <x:c r="I17" s="21"/>
+      <x:c r="I17" s="26"/>
       <x:c r="J17" s="26"/>
       <x:c r="K17" s="21"/>
     </x:row>
@@ -771,7 +835,7 @@
       <x:c r="F18" s="21"/>
       <x:c r="G18" s="21"/>
       <x:c r="H18" s="24"/>
-      <x:c r="I18" s="21"/>
+      <x:c r="I18" s="26"/>
       <x:c r="J18" s="26"/>
       <x:c r="K18" s="21"/>
     </x:row>
@@ -784,7 +848,7 @@
       <x:c r="F19" s="21"/>
       <x:c r="G19" s="21"/>
       <x:c r="H19" s="24"/>
-      <x:c r="I19" s="21"/>
+      <x:c r="I19" s="26"/>
       <x:c r="J19" s="26"/>
       <x:c r="K19" s="21"/>
     </x:row>
@@ -797,7 +861,7 @@
       <x:c r="F20" s="21"/>
       <x:c r="G20" s="21"/>
       <x:c r="H20" s="24"/>
-      <x:c r="I20" s="21"/>
+      <x:c r="I20" s="26"/>
       <x:c r="J20" s="26"/>
       <x:c r="K20" s="21"/>
     </x:row>
@@ -810,7 +874,7 @@
       <x:c r="F21" s="21"/>
       <x:c r="G21" s="21"/>
       <x:c r="H21" s="24"/>
-      <x:c r="I21" s="21"/>
+      <x:c r="I21" s="26"/>
       <x:c r="J21" s="26"/>
       <x:c r="K21" s="21"/>
     </x:row>
@@ -823,7 +887,7 @@
       <x:c r="F22" s="21"/>
       <x:c r="G22" s="21"/>
       <x:c r="H22" s="24"/>
-      <x:c r="I22" s="21"/>
+      <x:c r="I22" s="26"/>
       <x:c r="J22" s="26"/>
       <x:c r="K22" s="21"/>
     </x:row>
@@ -836,7 +900,7 @@
       <x:c r="F23" s="21"/>
       <x:c r="G23" s="21"/>
       <x:c r="H23" s="24"/>
-      <x:c r="I23" s="21"/>
+      <x:c r="I23" s="26"/>
       <x:c r="J23" s="26"/>
       <x:c r="K23" s="21"/>
     </x:row>
@@ -849,7 +913,7 @@
       <x:c r="F24" s="21"/>
       <x:c r="G24" s="21"/>
       <x:c r="H24" s="24"/>
-      <x:c r="I24" s="21"/>
+      <x:c r="I24" s="26"/>
       <x:c r="J24" s="26"/>
       <x:c r="K24" s="21"/>
     </x:row>
@@ -862,7 +926,7 @@
       <x:c r="F25" s="21"/>
       <x:c r="G25" s="21"/>
       <x:c r="H25" s="24"/>
-      <x:c r="I25" s="21"/>
+      <x:c r="I25" s="26"/>
       <x:c r="J25" s="26"/>
       <x:c r="K25" s="21"/>
     </x:row>
@@ -875,7 +939,7 @@
       <x:c r="F26" s="21"/>
       <x:c r="G26" s="21"/>
       <x:c r="H26" s="24"/>
-      <x:c r="I26" s="21"/>
+      <x:c r="I26" s="26"/>
       <x:c r="J26" s="26"/>
       <x:c r="K26" s="21"/>
     </x:row>
@@ -888,7 +952,7 @@
       <x:c r="F27" s="21"/>
       <x:c r="G27" s="21"/>
       <x:c r="H27" s="24"/>
-      <x:c r="I27" s="21"/>
+      <x:c r="I27" s="26"/>
       <x:c r="J27" s="26"/>
       <x:c r="K27" s="21"/>
     </x:row>
@@ -901,7 +965,7 @@
       <x:c r="F28" s="21"/>
       <x:c r="G28" s="21"/>
       <x:c r="H28" s="24"/>
-      <x:c r="I28" s="21"/>
+      <x:c r="I28" s="26"/>
       <x:c r="J28" s="26"/>
       <x:c r="K28" s="21"/>
     </x:row>
@@ -914,7 +978,7 @@
       <x:c r="F29" s="21"/>
       <x:c r="G29" s="21"/>
       <x:c r="H29" s="24"/>
-      <x:c r="I29" s="21"/>
+      <x:c r="I29" s="26"/>
       <x:c r="J29" s="26"/>
       <x:c r="K29" s="21"/>
     </x:row>
@@ -927,7 +991,7 @@
       <x:c r="F30" s="21"/>
       <x:c r="G30" s="21"/>
       <x:c r="H30" s="24"/>
-      <x:c r="I30" s="21"/>
+      <x:c r="I30" s="26"/>
       <x:c r="J30" s="26"/>
       <x:c r="K30" s="21"/>
     </x:row>
@@ -940,7 +1004,7 @@
       <x:c r="F31" s="21"/>
       <x:c r="G31" s="21"/>
       <x:c r="H31" s="24"/>
-      <x:c r="I31" s="21"/>
+      <x:c r="I31" s="26"/>
       <x:c r="J31" s="26"/>
       <x:c r="K31" s="21"/>
     </x:row>
@@ -953,7 +1017,7 @@
       <x:c r="F32" s="21"/>
       <x:c r="G32" s="21"/>
       <x:c r="H32" s="24"/>
-      <x:c r="I32" s="21"/>
+      <x:c r="I32" s="26"/>
       <x:c r="J32" s="26"/>
       <x:c r="K32" s="21"/>
     </x:row>
@@ -966,7 +1030,7 @@
       <x:c r="F33" s="21"/>
       <x:c r="G33" s="21"/>
       <x:c r="H33" s="24"/>
-      <x:c r="I33" s="21"/>
+      <x:c r="I33" s="26"/>
       <x:c r="J33" s="26"/>
       <x:c r="K33" s="21"/>
     </x:row>
@@ -979,7 +1043,7 @@
       <x:c r="F34" s="21"/>
       <x:c r="G34" s="21"/>
       <x:c r="H34" s="24"/>
-      <x:c r="I34" s="21"/>
+      <x:c r="I34" s="26"/>
       <x:c r="J34" s="26"/>
       <x:c r="K34" s="21"/>
     </x:row>
@@ -992,7 +1056,7 @@
       <x:c r="F35" s="21"/>
       <x:c r="G35" s="21"/>
       <x:c r="H35" s="24"/>
-      <x:c r="I35" s="21"/>
+      <x:c r="I35" s="26"/>
       <x:c r="J35" s="26"/>
       <x:c r="K35" s="21"/>
     </x:row>
@@ -1005,7 +1069,7 @@
       <x:c r="F36" s="21"/>
       <x:c r="G36" s="21"/>
       <x:c r="H36" s="24"/>
-      <x:c r="I36" s="21"/>
+      <x:c r="I36" s="26"/>
       <x:c r="J36" s="26"/>
       <x:c r="K36" s="21"/>
     </x:row>
@@ -1018,7 +1082,7 @@
       <x:c r="F37" s="21"/>
       <x:c r="G37" s="21"/>
       <x:c r="H37" s="24"/>
-      <x:c r="I37" s="21"/>
+      <x:c r="I37" s="26"/>
       <x:c r="J37" s="26"/>
       <x:c r="K37" s="21"/>
     </x:row>
@@ -1031,7 +1095,7 @@
       <x:c r="F38" s="21"/>
       <x:c r="G38" s="21"/>
       <x:c r="H38" s="24"/>
-      <x:c r="I38" s="21"/>
+      <x:c r="I38" s="26"/>
       <x:c r="J38" s="26"/>
       <x:c r="K38" s="21"/>
     </x:row>
@@ -1044,7 +1108,7 @@
       <x:c r="F39" s="21"/>
       <x:c r="G39" s="21"/>
       <x:c r="H39" s="24"/>
-      <x:c r="I39" s="21"/>
+      <x:c r="I39" s="26"/>
       <x:c r="J39" s="26"/>
       <x:c r="K39" s="21"/>
     </x:row>
@@ -1057,7 +1121,7 @@
       <x:c r="F40" s="21"/>
       <x:c r="G40" s="21"/>
       <x:c r="H40" s="24"/>
-      <x:c r="I40" s="21"/>
+      <x:c r="I40" s="26"/>
       <x:c r="J40" s="26"/>
       <x:c r="K40" s="21"/>
     </x:row>
@@ -1070,7 +1134,7 @@
       <x:c r="F41" s="21"/>
       <x:c r="G41" s="21"/>
       <x:c r="H41" s="24"/>
-      <x:c r="I41" s="21"/>
+      <x:c r="I41" s="26"/>
       <x:c r="J41" s="26"/>
       <x:c r="K41" s="21"/>
     </x:row>
@@ -1083,7 +1147,7 @@
       <x:c r="F42" s="21"/>
       <x:c r="G42" s="21"/>
       <x:c r="H42" s="24"/>
-      <x:c r="I42" s="21"/>
+      <x:c r="I42" s="26"/>
       <x:c r="J42" s="26"/>
       <x:c r="K42" s="21"/>
     </x:row>
@@ -1096,7 +1160,7 @@
       <x:c r="F43" s="21"/>
       <x:c r="G43" s="21"/>
       <x:c r="H43" s="24"/>
-      <x:c r="I43" s="21"/>
+      <x:c r="I43" s="26"/>
       <x:c r="J43" s="26"/>
       <x:c r="K43" s="21"/>
     </x:row>
@@ -1109,7 +1173,7 @@
       <x:c r="F44" s="21"/>
       <x:c r="G44" s="21"/>
       <x:c r="H44" s="24"/>
-      <x:c r="I44" s="21"/>
+      <x:c r="I44" s="26"/>
       <x:c r="J44" s="26"/>
       <x:c r="K44" s="21"/>
     </x:row>
@@ -1122,7 +1186,7 @@
       <x:c r="F45" s="21"/>
       <x:c r="G45" s="21"/>
       <x:c r="H45" s="24"/>
-      <x:c r="I45" s="21"/>
+      <x:c r="I45" s="26"/>
       <x:c r="J45" s="26"/>
       <x:c r="K45" s="21"/>
     </x:row>
@@ -1135,7 +1199,7 @@
       <x:c r="F46" s="21"/>
       <x:c r="G46" s="21"/>
       <x:c r="H46" s="24"/>
-      <x:c r="I46" s="21"/>
+      <x:c r="I46" s="26"/>
       <x:c r="J46" s="26"/>
       <x:c r="K46" s="21"/>
     </x:row>
@@ -1148,7 +1212,7 @@
       <x:c r="F47" s="21"/>
       <x:c r="G47" s="21"/>
       <x:c r="H47" s="24"/>
-      <x:c r="I47" s="21"/>
+      <x:c r="I47" s="26"/>
       <x:c r="J47" s="26"/>
       <x:c r="K47" s="21"/>
     </x:row>
@@ -1161,7 +1225,7 @@
       <x:c r="F48" s="21"/>
       <x:c r="G48" s="21"/>
       <x:c r="H48" s="24"/>
-      <x:c r="I48" s="21"/>
+      <x:c r="I48" s="26"/>
       <x:c r="J48" s="26"/>
       <x:c r="K48" s="21"/>
     </x:row>
@@ -1174,7 +1238,7 @@
       <x:c r="F49" s="21"/>
       <x:c r="G49" s="21"/>
       <x:c r="H49" s="24"/>
-      <x:c r="I49" s="21"/>
+      <x:c r="I49" s="26"/>
       <x:c r="J49" s="26"/>
       <x:c r="K49" s="21"/>
     </x:row>
@@ -1187,9 +1251,309 @@
       <x:c r="F50" s="21"/>
       <x:c r="G50" s="21"/>
       <x:c r="H50" s="24"/>
-      <x:c r="I50" s="21"/>
+      <x:c r="I50" s="26"/>
       <x:c r="J50" s="26"/>
       <x:c r="K50" s="21"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="E51" s="33"/>
+      <x:c r="H51" s="34"/>
+      <x:c r="I51" s="33"/>
+      <x:c r="J51" s="33"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="E52" s="33"/>
+      <x:c r="H52" s="34"/>
+      <x:c r="I52" s="33"/>
+      <x:c r="J52" s="33"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="E53" s="33"/>
+      <x:c r="H53" s="34"/>
+      <x:c r="I53" s="33"/>
+      <x:c r="J53" s="33"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="E54" s="33"/>
+      <x:c r="H54" s="34"/>
+      <x:c r="I54" s="33"/>
+      <x:c r="J54" s="33"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="E55" s="33"/>
+      <x:c r="H55" s="34"/>
+      <x:c r="I55" s="33"/>
+      <x:c r="J55" s="33"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="E56" s="33"/>
+      <x:c r="H56" s="34"/>
+      <x:c r="I56" s="33"/>
+      <x:c r="J56" s="33"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="E57" s="33"/>
+      <x:c r="H57" s="34"/>
+      <x:c r="I57" s="33"/>
+      <x:c r="J57" s="33"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="E58" s="33"/>
+      <x:c r="H58" s="34"/>
+      <x:c r="I58" s="33"/>
+      <x:c r="J58" s="33"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="E59" s="33"/>
+      <x:c r="H59" s="34"/>
+      <x:c r="I59" s="33"/>
+      <x:c r="J59" s="33"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="E60" s="33"/>
+      <x:c r="H60" s="34"/>
+      <x:c r="I60" s="33"/>
+      <x:c r="J60" s="33"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="E61" s="33"/>
+      <x:c r="H61" s="34"/>
+      <x:c r="I61" s="33"/>
+      <x:c r="J61" s="33"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="E62" s="33"/>
+      <x:c r="H62" s="34"/>
+      <x:c r="I62" s="33"/>
+      <x:c r="J62" s="33"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="E63" s="33"/>
+      <x:c r="H63" s="34"/>
+      <x:c r="I63" s="33"/>
+      <x:c r="J63" s="33"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="E64" s="33"/>
+      <x:c r="H64" s="34"/>
+      <x:c r="I64" s="33"/>
+      <x:c r="J64" s="33"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="E65" s="33"/>
+      <x:c r="H65" s="34"/>
+      <x:c r="I65" s="33"/>
+      <x:c r="J65" s="33"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="E66" s="33"/>
+      <x:c r="H66" s="34"/>
+      <x:c r="I66" s="33"/>
+      <x:c r="J66" s="33"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="E67" s="33"/>
+      <x:c r="H67" s="34"/>
+      <x:c r="I67" s="33"/>
+      <x:c r="J67" s="33"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="E68" s="33"/>
+      <x:c r="H68" s="34"/>
+      <x:c r="I68" s="33"/>
+      <x:c r="J68" s="33"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="E69" s="33"/>
+      <x:c r="H69" s="34"/>
+      <x:c r="I69" s="33"/>
+      <x:c r="J69" s="33"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="E70" s="33"/>
+      <x:c r="H70" s="34"/>
+      <x:c r="I70" s="33"/>
+      <x:c r="J70" s="33"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="E71" s="33"/>
+      <x:c r="H71" s="34"/>
+      <x:c r="I71" s="33"/>
+      <x:c r="J71" s="33"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="E72" s="33"/>
+      <x:c r="H72" s="34"/>
+      <x:c r="I72" s="33"/>
+      <x:c r="J72" s="33"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="E73" s="33"/>
+      <x:c r="H73" s="34"/>
+      <x:c r="I73" s="33"/>
+      <x:c r="J73" s="33"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="E74" s="33"/>
+      <x:c r="H74" s="34"/>
+      <x:c r="I74" s="33"/>
+      <x:c r="J74" s="33"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="E75" s="33"/>
+      <x:c r="H75" s="34"/>
+      <x:c r="I75" s="33"/>
+      <x:c r="J75" s="33"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="E76" s="33"/>
+      <x:c r="H76" s="34"/>
+      <x:c r="I76" s="33"/>
+      <x:c r="J76" s="33"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="E77" s="33"/>
+      <x:c r="H77" s="34"/>
+      <x:c r="I77" s="33"/>
+      <x:c r="J77" s="33"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="E78" s="33"/>
+      <x:c r="H78" s="34"/>
+      <x:c r="I78" s="33"/>
+      <x:c r="J78" s="33"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="E79" s="33"/>
+      <x:c r="H79" s="34"/>
+      <x:c r="I79" s="33"/>
+      <x:c r="J79" s="33"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="E80" s="33"/>
+      <x:c r="H80" s="34"/>
+      <x:c r="I80" s="33"/>
+      <x:c r="J80" s="33"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="E81" s="33"/>
+      <x:c r="H81" s="34"/>
+      <x:c r="I81" s="33"/>
+      <x:c r="J81" s="33"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="E82" s="33"/>
+      <x:c r="H82" s="34"/>
+      <x:c r="I82" s="33"/>
+      <x:c r="J82" s="33"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="E83" s="33"/>
+      <x:c r="H83" s="34"/>
+      <x:c r="I83" s="33"/>
+      <x:c r="J83" s="33"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="E84" s="33"/>
+      <x:c r="H84" s="34"/>
+      <x:c r="I84" s="33"/>
+      <x:c r="J84" s="33"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="E85" s="33"/>
+      <x:c r="H85" s="34"/>
+      <x:c r="I85" s="33"/>
+      <x:c r="J85" s="33"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="E86" s="33"/>
+      <x:c r="H86" s="34"/>
+      <x:c r="I86" s="33"/>
+      <x:c r="J86" s="33"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="E87" s="33"/>
+      <x:c r="H87" s="34"/>
+      <x:c r="I87" s="33"/>
+      <x:c r="J87" s="33"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="E88" s="33"/>
+      <x:c r="H88" s="34"/>
+      <x:c r="I88" s="33"/>
+      <x:c r="J88" s="33"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="E89" s="33"/>
+      <x:c r="H89" s="34"/>
+      <x:c r="I89" s="33"/>
+      <x:c r="J89" s="33"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="E90" s="33"/>
+      <x:c r="H90" s="34"/>
+      <x:c r="I90" s="33"/>
+      <x:c r="J90" s="33"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="E91" s="33"/>
+      <x:c r="H91" s="34"/>
+      <x:c r="I91" s="33"/>
+      <x:c r="J91" s="33"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="E92" s="33"/>
+      <x:c r="H92" s="34"/>
+      <x:c r="I92" s="33"/>
+      <x:c r="J92" s="33"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="E93" s="33"/>
+      <x:c r="H93" s="34"/>
+      <x:c r="I93" s="33"/>
+      <x:c r="J93" s="33"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="E94" s="33"/>
+      <x:c r="H94" s="34"/>
+      <x:c r="I94" s="33"/>
+      <x:c r="J94" s="33"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="E95" s="33"/>
+      <x:c r="H95" s="34"/>
+      <x:c r="I95" s="33"/>
+      <x:c r="J95" s="33"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="E96" s="33"/>
+      <x:c r="H96" s="34"/>
+      <x:c r="I96" s="33"/>
+      <x:c r="J96" s="33"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="E97" s="33"/>
+      <x:c r="H97" s="34"/>
+      <x:c r="I97" s="33"/>
+      <x:c r="J97" s="33"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="E98" s="33"/>
+      <x:c r="H98" s="34"/>
+      <x:c r="I98" s="33"/>
+      <x:c r="J98" s="33"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="E99" s="33"/>
+      <x:c r="H99" s="34"/>
+      <x:c r="I99" s="33"/>
+      <x:c r="J99" s="33"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="E100" s="33"/>
+      <x:c r="H100" s="34"/>
+      <x:c r="I100" s="33"/>
+      <x:c r="J100" s="33"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -1199,7 +1563,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e3d0c2554e74def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rded1b55ce54b4963"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1648,7 +2012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5f23a4640404ca2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R145df7bee8ca4b23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2642,7 +3006,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cc1c92d0484906"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a9cf617ee394fce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3311,7 +3675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a9a4a946a004703"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d60d61501f94ccb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3700,7 +4064,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R612b03cf89e54f26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R100ba7e438b24834"/>
   </x:tableParts>
 </x:worksheet>
 </file>